--- a/AI Audit Log_Đào Thị Thùy Trang .xlsx
+++ b/AI Audit Log_Đào Thị Thùy Trang .xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBE9ED71-AC63-4D79-AF84-902954BA87C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0979B43D-B226-4A3A-819B-D7BFF6E6D7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="2" r:id="rId1"/>
     <sheet name="Week1" sheetId="1" r:id="rId2"/>
     <sheet name="Week 2" sheetId="3" r:id="rId3"/>
+    <sheet name="Week3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -621,6 +622,72 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>UML Notation</t>
+  </si>
+  <si>
+    <t>“Ký hiệu UML chuẩn cho class diagram gồm những gì?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI mô tả class gồm tên class, attributes, operations và các đường quan hệ như association, aggregation, composition, inheritance.
+Kiểm chứng: Tôi đối chiếu với hình UML notation trong slide bài giảng.
+Quyết định: Sử dụng đúng ký hiệu UML chuẩn khi vẽ bằng draw.io hoặc PlantUML.</t>
+  </si>
+  <si>
+    <t>Context Modeling</t>
+  </si>
+  <si>
+    <t>“Hệ thống của nhóm có những external classes nào?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất external classes như Display Screen, Payment System, AI Engine, SMS Gateway.
+Kiểm chứng: Tôi so sánh với mô hình context diagram đã phân tích trước đó.
+Quyết định: Thêm các external system vào sơ đồ để mô tả tương tác hệ thống đầy đủ hơn.</t>
+  </si>
+  <si>
+    <t>Operations/Methods</t>
+  </si>
+  <si>
+    <t>“Mỗi class nên có phương thức gì?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các method như createTicket(), callNextQueue(), sendNotification(), login().
+Kiểm chứng: Tôi đối chiếu với chức năng hệ thống mà nhóm đã phân tích.
+Quyết định: Dùng các operation này để thể hiện hành vi của class trong UML.</t>
+  </si>
+  <si>
+    <t>Multiplicity</t>
+  </si>
+  <si>
+    <t>“Multiplicity trong class diagram được xác định như thế nào?”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích các ký hiệu 1..1, 1.., 0.. và ví dụ một Queue có nhiều Ticket.
+Kiểm chứng: Tôi đối chiếu với ký hiệu UML trong slide.
+Quyết định: Sử dụng multiplicity để biểu diễn số lượng đối tượng trong quan hệ.</t>
+  </si>
+  <si>
+    <t>PlantUML</t>
+  </si>
+  <si>
+    <t>“Hãy tạo code PlantUML cho class diagram của nhóm tôi”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh code PlantUML gồm các class, thuộc tính và quan hệ giữa các class.
+Kiểm chứng: Tôi copy code vào PlantUML để kiểm tra sơ đồ hiển thị đúng.
+Quyết định: Dùng PlantUML để chỉnh sửa và hoàn thiện class diagram của nhóm.</t>
+  </si>
+  <si>
+    <t>Kiểm tra &amp; hoàn thiện</t>
+  </si>
+  <si>
+    <t>“Kiểm tra giúp tôi class diagram đã đúng chuẩn UML chưa”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI kiểm tra các lỗi như thiếu multiplicity, sai quan hệ inheritance hoặc dùng sai composition/aggregation.
+Kiểm chứng: Tôi so sánh lại với slide UML và góp ý của giảng viên trên lớp.
+Quyết định: Chỉnh sửa sơ đồ theo góp ý để hoàn thiện bản cuối cùng nộp nhóm.</t>
   </si>
 </sst>
 </file>
@@ -804,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -824,6 +891,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -855,61 +982,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1248,79 +1321,79 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="17"/>
-    <col min="2" max="3" width="28.59765625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="46.5" style="17" customWidth="1"/>
-    <col min="5" max="16384" width="8.796875" style="17"/>
+    <col min="1" max="1" width="8.796875" style="8"/>
+    <col min="2" max="3" width="28.59765625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="46.5" style="8" customWidth="1"/>
+    <col min="5" max="16384" width="8.796875" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.6">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="69">
-      <c r="A2" s="18">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="55.2">
-      <c r="A3" s="18">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="69">
-      <c r="A4" s="18">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="82.8">
-      <c r="A5" s="18">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="10" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1356,13 +1429,13 @@
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="27.6">
-      <c r="A2" s="7">
+      <c r="A2" s="27">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="33" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -1370,27 +1443,27 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="8"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="14"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="34"/>
       <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:5" ht="42" thickBot="1">
-      <c r="A4" s="9"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="15"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27.6">
-      <c r="A5" s="7">
+      <c r="A5" s="27">
         <v>2</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="33" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -1398,27 +1471,27 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="8"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:5" ht="55.8" thickBot="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="15"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27.6">
-      <c r="A8" s="7">
+      <c r="A8" s="27">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="33" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -1426,27 +1499,27 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="8"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="14"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="34"/>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:5" ht="55.8" thickBot="1">
-      <c r="A10" s="9"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="15"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="7">
+      <c r="A11" s="27">
         <v>4</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="33" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -1454,300 +1527,21 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="8"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="14"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:5" ht="55.8" thickBot="1">
-      <c r="A13" s="9"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="15"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="5" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="1" width="8.796875" style="32"/>
-    <col min="2" max="4" width="34.296875" style="17" customWidth="1"/>
-    <col min="5" max="16384" width="8.796875" style="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="28.2" thickBot="1">
-      <c r="A1" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="27.6" customHeight="1">
-      <c r="A2" s="33">
-        <v>1</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="34"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="23"/>
-    </row>
-    <row r="4" spans="1:4" ht="42" thickBot="1">
-      <c r="A4" s="35"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="27.6" customHeight="1">
-      <c r="A5" s="33">
-        <v>2</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="34"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="23"/>
-    </row>
-    <row r="7" spans="1:4" ht="28.2" thickBot="1">
-      <c r="A7" s="35"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="27.6">
-      <c r="A8" s="33">
-        <v>3</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="34"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="23"/>
-    </row>
-    <row r="10" spans="1:4" ht="42" thickBot="1">
-      <c r="A10" s="35"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="27.6">
-      <c r="A11" s="33">
-        <v>4</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="34"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="23"/>
-    </row>
-    <row r="13" spans="1:4" ht="42" thickBot="1">
-      <c r="A13" s="35"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="27.6">
-      <c r="A14" s="33">
-        <v>5</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="34"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="23"/>
-    </row>
-    <row r="16" spans="1:4" ht="42" thickBot="1">
-      <c r="A16" s="35"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="27.6">
-      <c r="A17" s="33">
-        <v>6</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="34"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="23"/>
-    </row>
-    <row r="19" spans="1:4" ht="42" thickBot="1">
-      <c r="A19" s="35"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="27.6">
-      <c r="A20" s="33">
-        <v>7</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="34"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="23"/>
-    </row>
-    <row r="22" spans="1:4" ht="55.8" thickBot="1">
-      <c r="A22" s="35"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="41.4">
-      <c r="A23" s="33">
-        <v>8</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="34"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="23"/>
-    </row>
-    <row r="25" spans="1:4" ht="43.8" thickBot="1">
-      <c r="A25" s="35"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:C19"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="C8:C10"/>
@@ -1763,4 +1557,395 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="8.796875" style="17"/>
+    <col min="2" max="4" width="34.296875" style="8" customWidth="1"/>
+    <col min="5" max="16384" width="8.796875" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28.2" thickBot="1">
+      <c r="A1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A2" s="18">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="19"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="14"/>
+    </row>
+    <row r="4" spans="1:4" ht="42" thickBot="1">
+      <c r="A4" s="20"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.6" customHeight="1">
+      <c r="A5" s="18">
+        <v>2</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="19"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="14"/>
+    </row>
+    <row r="7" spans="1:4" ht="28.2" thickBot="1">
+      <c r="A7" s="20"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27.6">
+      <c r="A8" s="18">
+        <v>3</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="19"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="14"/>
+    </row>
+    <row r="10" spans="1:4" ht="28.2" thickBot="1">
+      <c r="A10" s="20"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="27.6">
+      <c r="A11" s="18">
+        <v>4</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="19"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="14"/>
+    </row>
+    <row r="13" spans="1:4" ht="42" thickBot="1">
+      <c r="A13" s="20"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.6">
+      <c r="A14" s="18">
+        <v>5</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="19"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="14"/>
+    </row>
+    <row r="16" spans="1:4" ht="42" thickBot="1">
+      <c r="A16" s="20"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="27.6">
+      <c r="A17" s="18">
+        <v>6</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="19"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="14"/>
+    </row>
+    <row r="19" spans="1:4" ht="42" thickBot="1">
+      <c r="A19" s="20"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="27.6">
+      <c r="A20" s="18">
+        <v>7</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="19"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="14"/>
+    </row>
+    <row r="22" spans="1:4" ht="55.8" thickBot="1">
+      <c r="A22" s="20"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="41.4">
+      <c r="A23" s="18">
+        <v>8</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="19"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="14"/>
+    </row>
+    <row r="25" spans="1:4" ht="43.8" thickBot="1">
+      <c r="A25" s="20"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:C25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E530F1-9FCF-4B6E-B20F-D69F9507D514}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="35.3984375" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="7.8984375" style="37" customWidth="1"/>
+    <col min="2" max="16384" width="35.3984375" style="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="27.6">
+      <c r="A1" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="124.2">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="110.4">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="96.6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="82.8">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="96.6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="96.6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>